--- a/GRE词根记忆表.xlsx
+++ b/GRE词根记忆表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\69450\projects\3000\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB902F77-1D39-45E7-A9C0-39891BC60633}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC67266D-7803-40D6-8CC3-7C4D97618DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,25 @@
     <sheet name="3天计划 Plan" sheetId="3" r:id="rId3"/>
     <sheet name="易混词根 Confusables" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="591">
   <si>
     <t>#</t>
   </si>
@@ -70,18 +83,12 @@
     <t>好,善</t>
   </si>
   <si>
-    <t>benevolent仁慈,benign良性,bonhomie友善</t>
-  </si>
-  <si>
     <t>mal</t>
   </si>
   <si>
     <t>坏,恶</t>
   </si>
   <si>
-    <t>malign诽谤,malevolent恶意,malady疾病</t>
-  </si>
-  <si>
     <t>magn / mega</t>
   </si>
   <si>
@@ -142,9 +149,6 @@
     <t>带来,生</t>
   </si>
   <si>
-    <t>proliferate激增,vociferous喧闹,fertile</t>
-  </si>
-  <si>
     <t>port</t>
   </si>
   <si>
@@ -155,9 +159,6 @@
   </si>
   <si>
     <t>拉,拖</t>
-  </si>
-  <si>
-    <t>intractable难驾驭,protract延长,detract贬低</t>
   </si>
   <si>
     <t>ject</t>
@@ -2186,6 +2187,435 @@
         <charset val="134"/>
       </rPr>
       <t>突然</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>malign</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>诽谤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,malevolent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>恶意</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,malady</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>疾病</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>benevolent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>仁慈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,benign</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>良性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,bonhomie</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>友善</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>proliferate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>激增</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,vociferous</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>喧闹</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,fertile</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>novel,innovate,renovate</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>disaster,astral</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>posit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>假定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,juxtapose</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>并置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,proponent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>支持者</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>remit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>免除</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,emit,intermittent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>间歇,undermit连续不断的</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>intractable</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>难驾驭</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,protract</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>延长</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,detract</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>贬低</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>aver</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>断言</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,avert</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>避免</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,inadvertent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>疏忽</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>fluent,confluence</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>汇合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,superfluous</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>多余</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>deflect</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偏转</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,inflection</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>变调</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>nascent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初生</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,innate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>天生</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,renaissance</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2651,7 +3081,7 @@
         <v>3</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2668,7 +3098,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -2682,78 +3112,78 @@
         <v>8</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="H3" s="8" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>553</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>580</v>
+      </c>
+      <c r="H6" s="6" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>562</v>
-      </c>
-      <c r="H4" s="8" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>557</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="7" t="s">
+    <row r="7" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="C7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>18</v>
+      <c r="D7" s="6" t="s">
+        <v>579</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>569</v>
+        <v>565</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -2761,16 +3191,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2778,84 +3208,84 @@
         <v>8</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="H9" s="8" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="C10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="D10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>557</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>554</v>
+      </c>
+      <c r="H12" s="6" t="s">
         <v>571</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>561</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="s">
+    <row r="13" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>558</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>559</v>
+      <c r="D13" s="6" t="s">
+        <v>555</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -2863,50 +3293,50 @@
         <v>13</v>
       </c>
       <c r="B14" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>556</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C15" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>560</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>14</v>
-      </c>
-      <c r="B15" s="7" t="s">
+      <c r="D15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="H15" s="6" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>39</v>
+        <v>36</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>581</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -2914,33 +3344,33 @@
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A18" s="7">
         <v>17</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C18" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>586</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>43</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -2948,50 +3378,50 @@
         <v>18</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H19" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A20" s="4">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D19" s="7" t="s">
+      <c r="D20" s="6" t="s">
+        <v>585</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="H19" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="7">
-        <v>19</v>
-      </c>
-      <c r="B20" s="7" t="s">
+      <c r="C21" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="7">
-        <v>20</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C21" s="7" t="s">
+      <c r="D21" s="6" t="s">
+        <v>584</v>
+      </c>
+      <c r="H21" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -2999,16 +3429,16 @@
         <v>21</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C22" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H22" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -3016,67 +3446,67 @@
         <v>22</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C23" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>587</v>
+      </c>
+      <c r="H24" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D24" s="7" t="s">
+      <c r="D25" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H24" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="7">
-        <v>24</v>
-      </c>
-      <c r="B25" s="7" t="s">
+      <c r="C26" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="7">
-        <v>25</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C26" s="7" t="s">
+      <c r="D26" s="6" t="s">
+        <v>589</v>
+      </c>
+      <c r="H26" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="27" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -3084,16 +3514,16 @@
         <v>26</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C27" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>578</v>
+      </c>
+      <c r="H27" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>582</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -3101,16 +3531,16 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -3118,16 +3548,16 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>75</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -3135,16 +3565,16 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H30" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="25" x14ac:dyDescent="0.25">
@@ -3152,16 +3582,16 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C31" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -3169,16 +3599,16 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H32" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -3186,16 +3616,16 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="H33" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -3203,16 +3633,16 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C34" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="H34" s="3" t="s">
         <v>89</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -3220,16 +3650,16 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="H35" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -3237,16 +3667,16 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C36" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H36" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -3254,16 +3684,16 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="H37" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -3271,16 +3701,16 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C38" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H38" s="3" t="s">
         <v>101</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -3288,16 +3718,16 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H39" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:8" ht="25" x14ac:dyDescent="0.25">
@@ -3305,16 +3735,16 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H40" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -3322,16 +3752,16 @@
         <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="H41" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -3339,16 +3769,16 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C42" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -3356,16 +3786,16 @@
         <v>42</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="H43" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -3373,16 +3803,16 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C44" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -3390,16 +3820,16 @@
         <v>44</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C45" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="H45" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -3407,16 +3837,16 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H46" s="3" t="s">
         <v>124</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -3424,16 +3854,16 @@
         <v>46</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="H47" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -3441,16 +3871,16 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C48" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H48" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -3458,16 +3888,16 @@
         <v>48</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C49" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="H49" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -3475,16 +3905,16 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C50" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H50" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -3492,16 +3922,16 @@
         <v>50</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="H51" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -3509,16 +3939,16 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C52" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H52" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -3526,16 +3956,16 @@
         <v>52</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H53" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -3543,16 +3973,16 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C54" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H54" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -3560,16 +3990,16 @@
         <v>54</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="H55" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -3577,16 +4007,16 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C56" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H56" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -3594,16 +4024,16 @@
         <v>56</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C57" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="H57" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="H57" s="2" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -3611,16 +4041,16 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="H58" s="3" t="s">
         <v>160</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -3628,16 +4058,16 @@
         <v>58</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="C59" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="H59" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="H59" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -3645,16 +4075,16 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C60" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="H60" s="3" t="s">
         <v>166</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -3662,16 +4092,16 @@
         <v>60</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C61" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="H61" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -3679,16 +4109,16 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="C62" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H62" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -3696,16 +4126,16 @@
         <v>62</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C63" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="H63" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H63" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -3713,16 +4143,16 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C64" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="H64" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -3730,16 +4160,16 @@
         <v>64</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="C65" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H65" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -3747,16 +4177,16 @@
         <v>65</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H66" s="3" t="s">
         <v>184</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="H66" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -3764,16 +4194,16 @@
         <v>66</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="C67" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H67" s="2" t="s">
         <v>187</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -3781,16 +4211,16 @@
         <v>67</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C68" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H68" s="3" t="s">
         <v>190</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H68" s="3" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -3798,16 +4228,16 @@
         <v>68</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C69" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="H69" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -3815,16 +4245,16 @@
         <v>69</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C70" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H70" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H70" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -3832,16 +4262,16 @@
         <v>70</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C71" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H71" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="H71" s="2" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -3849,16 +4279,16 @@
         <v>71</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="C72" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="H72" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="H72" s="3" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -3866,16 +4296,16 @@
         <v>72</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="C73" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="H73" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="25" x14ac:dyDescent="0.25">
@@ -3883,16 +4313,16 @@
         <v>73</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C74" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="H74" s="3" t="s">
         <v>208</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="H74" s="3" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -3900,16 +4330,16 @@
         <v>74</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="C75" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H75" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -3917,16 +4347,16 @@
         <v>75</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C76" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="H76" s="3" t="s">
         <v>214</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="H76" s="3" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -3934,16 +4364,16 @@
         <v>76</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="C77" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="H77" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="H77" s="2" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -3951,16 +4381,16 @@
         <v>77</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C78" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="H78" s="3" t="s">
         <v>220</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="H78" s="3" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -3968,50 +4398,50 @@
         <v>78</v>
       </c>
       <c r="B79" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="4">
+        <v>79</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="C80" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D79" s="3" t="s">
+      <c r="D80" s="6" t="s">
+        <v>583</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="4">
+        <v>80</v>
+      </c>
+      <c r="B81" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="H79" s="2" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="2">
-        <v>79</v>
-      </c>
-      <c r="B80" s="2" t="s">
+      <c r="C81" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="C80" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="3">
-        <v>80</v>
-      </c>
-      <c r="B81" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="C81" s="3" t="s">
+      <c r="D81" s="6" t="s">
+        <v>582</v>
+      </c>
+      <c r="H81" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="H81" s="2" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -4019,16 +4449,16 @@
         <v>81</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="C82" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="H82" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -4036,16 +4466,16 @@
         <v>82</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C83" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H83" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -4053,33 +4483,33 @@
         <v>83</v>
       </c>
       <c r="B84" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A85" s="7">
+        <v>84</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C85" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="C84" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="3">
-        <v>84</v>
-      </c>
-      <c r="B85" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="C85" s="3" t="s">
+      <c r="D85" s="8" t="s">
+        <v>590</v>
+      </c>
+      <c r="H85" s="7" t="s">
         <v>241</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="H85" s="2" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -4087,16 +4517,16 @@
         <v>85</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C86" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="H86" s="3" t="s">
         <v>244</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="25" x14ac:dyDescent="0.25">
@@ -4104,16 +4534,16 @@
         <v>86</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C87" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H87" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -4121,16 +4551,16 @@
         <v>87</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="C88" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="H88" s="3" t="s">
         <v>250</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -4138,16 +4568,16 @@
         <v>88</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C89" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="H89" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -4155,16 +4585,16 @@
         <v>89</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C90" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="H90" s="3" t="s">
         <v>256</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -4172,16 +4602,16 @@
         <v>90</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C91" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="H91" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -4189,16 +4619,16 @@
         <v>91</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C92" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="H92" s="3" t="s">
         <v>262</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -4206,16 +4636,16 @@
         <v>92</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="C93" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="H93" s="2" t="s">
         <v>265</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
@@ -4223,16 +4653,16 @@
         <v>93</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C94" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="H94" s="3" t="s">
         <v>268</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
@@ -4240,16 +4670,16 @@
         <v>94</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="C95" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="H95" s="2" t="s">
         <v>271</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="H95" s="2" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
@@ -4257,16 +4687,16 @@
         <v>95</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C96" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="H96" s="3" t="s">
         <v>274</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
@@ -4274,16 +4704,16 @@
         <v>96</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="C97" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="H97" s="2" t="s">
         <v>277</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
@@ -4291,16 +4721,16 @@
         <v>97</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C98" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="H98" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
@@ -4308,16 +4738,16 @@
         <v>98</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C99" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="H99" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
@@ -4325,16 +4755,16 @@
         <v>99</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="C100" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H100" s="3" t="s">
         <v>286</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -4342,16 +4772,16 @@
         <v>100</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C101" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="H101" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="H101" s="2" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -4359,16 +4789,16 @@
         <v>101</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="C102" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="H102" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -4376,16 +4806,16 @@
         <v>102</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C103" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H103" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="H103" s="2" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -4393,16 +4823,16 @@
         <v>103</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C104" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="H104" s="3" t="s">
         <v>298</v>
-      </c>
-      <c r="D104" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -4410,16 +4840,16 @@
         <v>104</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C105" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="H105" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="H105" s="2" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -4427,16 +4857,16 @@
         <v>105</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C106" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="H106" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="D106" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -4444,16 +4874,16 @@
         <v>106</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C107" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="H107" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="H107" s="2" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
@@ -4461,16 +4891,16 @@
         <v>107</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C108" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="H108" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
@@ -4478,16 +4908,16 @@
         <v>108</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C109" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="H109" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="H109" s="2" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
@@ -4495,16 +4925,16 @@
         <v>109</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C110" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="H110" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
@@ -4512,16 +4942,16 @@
         <v>110</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C111" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="H111" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="H111" s="2" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
@@ -4529,16 +4959,16 @@
         <v>111</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C112" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="H112" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="H112" s="3" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
@@ -4546,16 +4976,16 @@
         <v>112</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C113" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="H113" s="2" t="s">
         <v>325</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="H113" s="2" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
@@ -4563,16 +4993,16 @@
         <v>113</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C114" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="H114" s="3" t="s">
         <v>328</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
@@ -4580,16 +5010,16 @@
         <v>114</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C115" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="H115" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="H115" s="2" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
@@ -4597,16 +5027,16 @@
         <v>115</v>
       </c>
       <c r="B116" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="H116" s="3" t="s">
         <v>333</v>
-      </c>
-      <c r="C116" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="D116" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="H116" s="3" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
@@ -4614,16 +5044,16 @@
         <v>116</v>
       </c>
       <c r="B117" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="H117" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="C117" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H117" s="2" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
@@ -4631,16 +5061,16 @@
         <v>117</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C118" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="H118" s="3" t="s">
         <v>339</v>
-      </c>
-      <c r="D118" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
@@ -4648,16 +5078,16 @@
         <v>118</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C119" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="H119" s="2" t="s">
         <v>342</v>
-      </c>
-      <c r="D119" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="H119" s="2" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -4665,16 +5095,16 @@
         <v>119</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C120" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="H120" s="3" t="s">
         <v>345</v>
-      </c>
-      <c r="D120" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="25" x14ac:dyDescent="0.25">
@@ -4682,16 +5112,16 @@
         <v>120</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="C121" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="H121" s="2" t="s">
         <v>348</v>
-      </c>
-      <c r="D121" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="H121" s="2" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
@@ -4699,16 +5129,16 @@
         <v>121</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C122" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="H122" s="3" t="s">
         <v>351</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="H122" s="3" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
@@ -4716,16 +5146,16 @@
         <v>122</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="C123" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H123" s="2" t="s">
         <v>354</v>
-      </c>
-      <c r="D123" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="H123" s="2" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="25" x14ac:dyDescent="0.25">
@@ -4733,16 +5163,16 @@
         <v>123</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C124" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="H124" s="3" t="s">
         <v>357</v>
-      </c>
-      <c r="D124" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -4750,16 +5180,16 @@
         <v>124</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C125" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="H125" s="2" t="s">
         <v>360</v>
-      </c>
-      <c r="D125" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="H125" s="2" t="s">
-        <v>364</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -4767,16 +5197,16 @@
         <v>125</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C126" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="H126" s="3" t="s">
         <v>363</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="H126" s="3" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
@@ -4784,16 +5214,16 @@
         <v>126</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="C127" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="H127" s="2" t="s">
         <v>366</v>
-      </c>
-      <c r="D127" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="H127" s="2" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
@@ -4801,16 +5231,16 @@
         <v>127</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C128" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="H128" s="3" t="s">
         <v>369</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="H128" s="3" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
@@ -4818,16 +5248,16 @@
         <v>128</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C129" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="H129" s="2" t="s">
         <v>372</v>
-      </c>
-      <c r="D129" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="H129" s="2" t="s">
-        <v>376</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
@@ -4835,16 +5265,16 @@
         <v>129</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C130" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="H130" s="3" t="s">
         <v>375</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="H130" s="3" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -4852,13 +5282,13 @@
         <v>130</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
   </sheetData>
@@ -4883,13 +5313,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -4897,13 +5327,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -4911,13 +5341,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -4925,13 +5355,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -4939,13 +5369,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -4953,13 +5383,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -4967,13 +5397,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -4981,13 +5411,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -4995,13 +5425,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5009,13 +5439,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -5023,13 +5453,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -5037,13 +5467,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -5051,13 +5481,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -5065,13 +5495,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -5079,13 +5509,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -5093,13 +5523,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -5107,13 +5537,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -5121,13 +5551,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -5135,13 +5565,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -5149,13 +5579,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -5163,13 +5593,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -5177,13 +5607,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -5191,13 +5621,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -5205,13 +5635,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -5219,13 +5649,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -5233,13 +5663,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -5247,13 +5677,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -5261,13 +5691,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -5275,13 +5705,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -5289,13 +5719,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -5303,13 +5733,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5317,13 +5747,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -5331,13 +5761,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -5345,13 +5775,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -5359,13 +5789,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -5373,13 +5803,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -5387,13 +5817,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -5401,13 +5831,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -5415,13 +5845,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -5443,142 +5873,142 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
     </row>
   </sheetData>
@@ -5599,113 +6029,113 @@
   <sheetData>
     <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
     </row>
   </sheetData>

--- a/GRE词根记忆表.xlsx
+++ b/GRE词根记忆表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\69450\projects\3000\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC67266D-7803-40D6-8CC3-7C4D97618DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2AFDED-CB2B-4913-9174-CC7810F140BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="591">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="611">
   <si>
     <t>#</t>
   </si>
@@ -1155,9 +1155,6 @@
   </si>
   <si>
     <t>perennial常年,annual,millennium</t>
-  </si>
-  <si>
-    <t>mens / meter</t>
   </si>
   <si>
     <t>测量,月</t>
@@ -2616,6 +2613,952 @@
         <family val="2"/>
       </rPr>
       <t>,renaissance</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mens / meter</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>commensurate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>相称</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,immense</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>perennial</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>常年</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,annual,millennium</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>N/A</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>tious/ious/tous</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>adventitious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>外来的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>bumptious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>自以为是的,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>conscientious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有良心的,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>contentious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>引起争议的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>facetious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>喜欢开玩笑的轻浮的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>fictitious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>虚构的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>fractious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>难以管束的易怒的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>licentious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>放荡的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>ostentatious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>炫耀的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>pretentious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>喜欢炫耀的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>propitious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吉祥，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>rambunctious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>喧闹的骚乱的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>repetitious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>重复的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>seditious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>煽动的制造混乱的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>surreptitious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>偷偷摸摸的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>tendentious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有偏见的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>unpretentious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>谦逊的低调的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>captious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>吹毛求疵的爱挑毛病的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>sententious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>说教的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>auspicious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>好兆头的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>protentous</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不吉利的</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>religious,obligate,oblige</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>fallacious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>谬误</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,infallible</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>绝无错</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,fallible</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ambiguous</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>模糊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,ambivalent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>矛盾</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,ambidextrous</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>sentient</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有知觉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,dissent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>异议</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,assent</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>同意</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>obsequious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>谄媚</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,sequela</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>后遗症</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>gregarious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>合群</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,egregious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>极坏</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,segregate</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>equanimity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>沉着</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,equivocate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>含糊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,iniquity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>邪恶</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>florid</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>华丽</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,flourish</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>繁荣</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,efflorescence</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>sociable,dissociate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>分离</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>perjure</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>伪证</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,adjudicate</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>裁决</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,judicious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>明智</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>incipient</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>初期</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,susceptible</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>易受影响</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>prescient</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>预知</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,conscientious</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>尽责</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>vigilant</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>警惕</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>,vigil</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>守夜</t>
+    </r>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>cumb / cub</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>circumlocution</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>冗长，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>circumscribe</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>限制，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>circumspect</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小心地谨慎的，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>cumbersome</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="宋体"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>繁重冗长的难处理的，</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -2673,7 +3616,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2702,8 +3645,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -2726,11 +3681,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -2755,6 +3721,26 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3057,7 +4043,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H131"/>
+  <dimension ref="A1:H133"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -3081,7 +4067,7 @@
         <v>3</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3098,7 +4084,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -3112,10 +4098,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="4" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -3129,10 +4115,10 @@
         <v>10</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -3146,10 +4132,10 @@
         <v>12</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -3163,10 +4149,10 @@
         <v>14</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -3180,10 +4166,10 @@
         <v>16</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -3197,10 +4183,10 @@
         <v>18</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3217,7 +4203,7 @@
         <v>21</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3234,7 +4220,7 @@
         <v>24</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="11" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -3248,10 +4234,10 @@
         <v>23</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="12" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -3265,10 +4251,10 @@
         <v>27</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="13" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -3282,10 +4268,10 @@
         <v>29</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="14" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -3299,10 +4285,10 @@
         <v>31</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="15" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -3319,7 +4305,7 @@
         <v>34</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="16" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -3333,10 +4319,10 @@
         <v>36</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="17" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -3350,10 +4336,10 @@
         <v>38</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="18" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
@@ -3367,7 +4353,7 @@
         <v>40</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>43</v>
@@ -3401,7 +4387,7 @@
         <v>45</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>49</v>
@@ -3418,26 +4404,26 @@
         <v>48</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="22" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="7">
+    <row r="22" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A22" s="4">
         <v>21</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H22" s="7" t="s">
+      <c r="D22" s="6" t="s">
+        <v>606</v>
+      </c>
+      <c r="H22" s="4" t="s">
         <v>55</v>
       </c>
     </row>
@@ -3469,7 +4455,7 @@
         <v>57</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H24" s="7" t="s">
         <v>61</v>
@@ -3486,7 +4472,7 @@
         <v>60</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>64</v>
@@ -3503,7 +4489,7 @@
         <v>63</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>67</v>
@@ -3520,7 +4506,7 @@
         <v>66</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>70</v>
@@ -3645,20 +4631,20 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="3">
+    <row r="35" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
         <v>34</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C35" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="H35" s="2" t="s">
+      <c r="D35" s="6" t="s">
+        <v>599</v>
+      </c>
+      <c r="H35" s="4" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3730,20 +4716,20 @@
         <v>103</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="25" x14ac:dyDescent="0.25">
-      <c r="A40" s="2">
+    <row r="40" spans="1:8" s="16" customFormat="1" ht="25" x14ac:dyDescent="0.25">
+      <c r="A40" s="15">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
+      <c r="B40" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="C40" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="H40" s="3" t="s">
+      <c r="D40" s="17" t="s">
+        <v>607</v>
+      </c>
+      <c r="H40" s="15" t="s">
         <v>106</v>
       </c>
     </row>
@@ -3883,37 +4869,37 @@
         <v>130</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="3">
+    <row r="49" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A49" s="7">
         <v>48</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C49" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="H49" s="2" t="s">
+      <c r="D49" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="H49" s="7" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="2">
+    <row r="50" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A50" s="7">
         <v>49</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="C50" s="2" t="s">
+      <c r="C50" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="D50" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="H50" s="3" t="s">
+      <c r="D50" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="H50" s="7" t="s">
         <v>136</v>
       </c>
     </row>
@@ -4087,71 +5073,71 @@
         <v>166</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="3">
+    <row r="61" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A61" s="7">
         <v>60</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B61" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C61" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="H61" s="2" t="s">
+      <c r="D61" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="H61" s="7" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="2">
+    <row r="62" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A62" s="7">
         <v>61</v>
       </c>
-      <c r="B62" s="2" t="s">
+      <c r="B62" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="C62" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="D62" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="H62" s="3" t="s">
+      <c r="D62" s="8" t="s">
+        <v>601</v>
+      </c>
+      <c r="H62" s="7" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="3">
+    <row r="63" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A63" s="7">
         <v>62</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B63" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="C63" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="H63" s="2" t="s">
+      <c r="D63" s="8" t="s">
+        <v>604</v>
+      </c>
+      <c r="H63" s="7" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="2">
+    <row r="64" spans="1:8" s="9" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="7">
         <v>63</v>
       </c>
-      <c r="B64" s="2" t="s">
+      <c r="B64" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="C64" s="2" t="s">
+      <c r="C64" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="H64" s="3" t="s">
+      <c r="D64" s="8" t="s">
+        <v>605</v>
+      </c>
+      <c r="H64" s="7" t="s">
         <v>178</v>
       </c>
     </row>
@@ -4421,7 +5407,7 @@
         <v>222</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H80" s="4" t="s">
         <v>226</v>
@@ -4438,7 +5424,7 @@
         <v>225</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H81" s="4" t="s">
         <v>229</v>
@@ -4506,7 +5492,7 @@
         <v>237</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H85" s="7" t="s">
         <v>241</v>
@@ -4614,20 +5600,20 @@
         <v>259</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="2">
+    <row r="92" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A92" s="7">
         <v>91</v>
       </c>
-      <c r="B92" s="2" t="s">
+      <c r="B92" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="C92" s="2" t="s">
+      <c r="C92" s="7" t="s">
         <v>258</v>
       </c>
-      <c r="D92" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="H92" s="3" t="s">
+      <c r="D92" s="8" t="s">
+        <v>598</v>
+      </c>
+      <c r="H92" s="7" t="s">
         <v>262</v>
       </c>
     </row>
@@ -4682,20 +5668,20 @@
         <v>271</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="2">
+    <row r="96" spans="1:8" s="5" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A96" s="4">
         <v>95</v>
       </c>
-      <c r="B96" s="2" t="s">
+      <c r="B96" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="C96" s="2" t="s">
+      <c r="C96" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="H96" s="3" t="s">
+      <c r="D96" s="6" t="s">
+        <v>597</v>
+      </c>
+      <c r="H96" s="4" t="s">
         <v>274</v>
       </c>
     </row>
@@ -4767,20 +5753,20 @@
         <v>286</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="3">
+    <row r="101" spans="1:8" s="9" customFormat="1" ht="14.5" x14ac:dyDescent="0.25">
+      <c r="A101" s="7">
         <v>100</v>
       </c>
-      <c r="B101" s="3" t="s">
+      <c r="B101" s="7" t="s">
         <v>284</v>
       </c>
-      <c r="C101" s="3" t="s">
+      <c r="C101" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="H101" s="2" t="s">
+      <c r="D101" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="H101" s="7" t="s">
         <v>289</v>
       </c>
     </row>
@@ -5056,20 +6042,20 @@
         <v>336</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="2">
+    <row r="118" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="4">
         <v>117</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="B118" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="D118" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="H118" s="3" t="s">
+      <c r="H118" s="4" t="s">
         <v>339</v>
       </c>
     </row>
@@ -5141,20 +6127,20 @@
         <v>351</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="3">
+    <row r="123" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A123" s="4">
         <v>122</v>
       </c>
-      <c r="B123" s="3" t="s">
+      <c r="B123" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="C123" s="3" t="s">
+      <c r="C123" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="D123" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="H123" s="2" t="s">
+      <c r="D123" s="6" t="s">
+        <v>596</v>
+      </c>
+      <c r="H123" s="4" t="s">
         <v>354</v>
       </c>
     </row>
@@ -5260,7 +6246,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -5270,25 +6256,53 @@
       <c r="C130" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="D130" s="2" t="s">
-        <v>372</v>
+      <c r="D130" s="14" t="s">
+        <v>592</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="14.5" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
         <v>130</v>
       </c>
-      <c r="B131" s="3" t="s">
+      <c r="B131" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="C131" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="C131" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="D131" s="3" t="s">
-        <v>375</v>
+      <c r="D131" s="10" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" s="12" customFormat="1" ht="79.5" x14ac:dyDescent="0.25">
+      <c r="A132" s="11">
+        <v>131</v>
+      </c>
+      <c r="B132" s="13" t="s">
+        <v>594</v>
+      </c>
+      <c r="C132" s="13" t="s">
+        <v>593</v>
+      </c>
+      <c r="D132" s="13" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" s="12" customFormat="1" ht="26" x14ac:dyDescent="0.25">
+      <c r="A133" s="11">
+        <v>132</v>
+      </c>
+      <c r="B133" s="13" t="s">
+        <v>609</v>
+      </c>
+      <c r="C133" s="13" t="s">
+        <v>593</v>
+      </c>
+      <c r="D133" s="13" t="s">
+        <v>610</v>
       </c>
     </row>
   </sheetData>
@@ -5313,13 +6327,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -5327,13 +6341,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>379</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -5341,13 +6355,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>382</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -5355,13 +6369,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -5369,13 +6383,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>388</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -5383,13 +6397,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -5397,13 +6411,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>394</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -5411,13 +6425,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>398</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -5425,13 +6439,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>400</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>401</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -5439,13 +6453,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -5453,13 +6467,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>406</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>407</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -5467,13 +6481,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>410</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -5481,13 +6495,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>412</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -5495,13 +6509,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>416</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -5509,13 +6523,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>418</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -5523,13 +6537,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>422</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -5537,13 +6551,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>424</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -5551,13 +6565,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -5565,13 +6579,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>430</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -5579,13 +6593,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -5593,13 +6607,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>436</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -5607,13 +6621,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -5621,13 +6635,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>16</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -5635,13 +6649,13 @@
         <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>445</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -5649,13 +6663,13 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>447</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>448</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -5663,13 +6677,13 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -5677,13 +6691,13 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>453</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -5691,13 +6705,13 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -5705,13 +6719,13 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="D29" s="3" t="s">
         <v>459</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>460</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -5719,13 +6733,13 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -5733,13 +6747,13 @@
         <v>30</v>
       </c>
       <c r="B31" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C31" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="D31" s="3" t="s">
         <v>465</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -5747,13 +6761,13 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="D32" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -5761,13 +6775,13 @@
         <v>32</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>471</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>472</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -5775,13 +6789,13 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="D34" s="2" t="s">
         <v>474</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -5789,13 +6803,13 @@
         <v>34</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="D35" s="3" t="s">
         <v>477</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -5803,13 +6817,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="C36" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="C36" s="2" t="s">
+      <c r="D36" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -5817,13 +6831,13 @@
         <v>36</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="D37" s="3" t="s">
         <v>483</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -5831,13 +6845,13 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -5845,13 +6859,13 @@
         <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="D39" s="3" t="s">
         <v>489</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>490</v>
       </c>
     </row>
   </sheetData>
@@ -5873,13 +6887,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>491</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>492</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>493</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>23</v>
@@ -5887,128 +6901,128 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>494</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>496</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>500</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>504</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>506</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>514</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="C8" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>520</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>523</v>
-      </c>
       <c r="D10" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -6029,113 +7043,113 @@
   <sheetData>
     <row r="1" spans="1:3" ht="22" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>531</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>533</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>534</v>
       </c>
       <c r="C4" s="2"/>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>535</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>536</v>
       </c>
       <c r="C5" s="3"/>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>538</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>540</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>541</v>
       </c>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>543</v>
       </c>
       <c r="C8" s="2"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>544</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>545</v>
       </c>
       <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>547</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>550</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>551</v>
       </c>
     </row>
   </sheetData>
